--- a/data/evacuation_space/data.xlsx
+++ b/data/evacuation_space/data.xlsx
@@ -8257,7 +8257,7 @@
         <v>134.0091222</v>
       </c>
       <c r="D134" t="str">
-        <v>香南小学校</v>
+        <v>香南小学校（※新校舎及び旧体育館を使用）</v>
       </c>
       <c r="E134" t="str">
         <v>高松市香南町横井1008</v>
@@ -11614,10 +11614,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="str">
-        <v>34.24461694</v>
+        <v>34.2416687</v>
       </c>
       <c r="C191" t="str">
-        <v>134.0055111</v>
+        <v>134.0069691</v>
       </c>
       <c r="D191" t="str">
         <v>月見ヶ原公園</v>
@@ -11915,7 +11915,7 @@
         <v>134.0344176254511</v>
       </c>
       <c r="D196" t="str">
-        <v>中央図書館</v>
+        <v>中央図書館(※改修工事中のため当面の間使用不可)</v>
       </c>
       <c r="E196" t="str">
         <v>昭和町一丁目2-20</v>

--- a/data/evacuation_space/data.xlsx
+++ b/data/evacuation_space/data.xlsx
@@ -8251,13 +8251,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>34.24104222</v>
+        <v>34.24334472104222</v>
       </c>
       <c r="C134" t="str">
-        <v>134.0091222</v>
+        <v>134.0085636</v>
       </c>
       <c r="D134" t="str">
-        <v>香南小学校（※新校舎及び旧体育館を使用）</v>
+        <v>香南小学校（※香南小学校跡地体育館を使用）</v>
       </c>
       <c r="E134" t="str">
         <v>高松市香南町横井1008</v>

--- a/data/evacuation_space/data.xlsx
+++ b/data/evacuation_space/data.xlsx
@@ -570,7 +570,7 @@
         <v>2.9</v>
       </c>
       <c r="R3" t="str">
-        <v>429</v>
+        <v>1530</v>
       </c>
       <c r="S3" t="str">
         <v>二番丁地区コミュニティ協議会</v>
@@ -688,7 +688,7 @@
         <v>4.1</v>
       </c>
       <c r="R5" t="str">
-        <v>351</v>
+        <v>1257</v>
       </c>
       <c r="S5" t="str">
         <v>亀阜校区コミュニティ協議会</v>
@@ -747,7 +747,7 @@
         <v>6.2</v>
       </c>
       <c r="R6" t="str">
-        <v>429</v>
+        <v>1956</v>
       </c>
       <c r="S6" t="str">
         <v>栗林校区コミュニティ協議会</v>
@@ -806,7 +806,7 @@
         <v>2.5</v>
       </c>
       <c r="R7" t="str">
-        <v>310</v>
+        <v>908</v>
       </c>
       <c r="S7" t="str">
         <v>花園地区コミュニティ協議会</v>
@@ -983,7 +983,7 @@
         <v>16.3</v>
       </c>
       <c r="R10" t="str">
-        <v>306</v>
+        <v>906</v>
       </c>
       <c r="S10" t="str">
         <v>鶴尾校区コミュニティ協議会</v>
@@ -1042,7 +1042,7 @@
         <v>13.2</v>
       </c>
       <c r="R11" t="str">
-        <v>393</v>
+        <v>1221</v>
       </c>
       <c r="S11" t="str">
         <v>太田地区コミュニティ協議会</v>
@@ -1101,7 +1101,7 @@
         <v>19.9</v>
       </c>
       <c r="R12" t="str">
-        <v>393</v>
+        <v>1436</v>
       </c>
       <c r="S12" t="str">
         <v>太田南地区コミュニティ協議会</v>
@@ -1160,7 +1160,7 @@
         <v>9.8</v>
       </c>
       <c r="R13" t="str">
-        <v>306</v>
+        <v>1305</v>
       </c>
       <c r="S13" t="str">
         <v>太田地区コミュニティ協議会</v>
@@ -1219,7 +1219,7 @@
         <v>1.7</v>
       </c>
       <c r="R14" t="str">
-        <v>324</v>
+        <v>1281</v>
       </c>
       <c r="S14" t="str">
         <v>木太地区コミュニティ協議会</v>
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="str">
-        <v>274</v>
+        <v>1221</v>
       </c>
       <c r="S15" t="str">
         <v>木太地区コミュニティ協議会</v>
@@ -1337,7 +1337,7 @@
         <v>3.2</v>
       </c>
       <c r="R16" t="str">
-        <v>324</v>
+        <v>1197</v>
       </c>
       <c r="S16" t="str">
         <v>木太地区コミュニティ協議会</v>
@@ -1396,7 +1396,7 @@
         <v>4.1</v>
       </c>
       <c r="R17" t="str">
-        <v>314</v>
+        <v>1302</v>
       </c>
       <c r="S17" t="str">
         <v>古高松地区コミュニティ協議会</v>
@@ -1455,7 +1455,7 @@
         <v>3.3</v>
       </c>
       <c r="R18" t="str">
-        <v>277</v>
+        <v>882</v>
       </c>
       <c r="S18" t="str">
         <v>古高松地区コミュニティ協議会</v>
@@ -1514,7 +1514,7 @@
         <v>16.4</v>
       </c>
       <c r="R19" t="str">
-        <v>405</v>
+        <v>1336</v>
       </c>
       <c r="S19" t="str">
         <v>屋島地区コミュニティ協議会</v>
@@ -1573,7 +1573,7 @@
         <v>2.7</v>
       </c>
       <c r="R20" t="str">
-        <v>396</v>
+        <v>1246</v>
       </c>
       <c r="S20" t="str">
         <v>屋島地区コミュニティ協議会</v>
@@ -1632,7 +1632,7 @@
         <v>2.5</v>
       </c>
       <c r="R21" t="str">
-        <v>247</v>
+        <v>471</v>
       </c>
       <c r="S21" t="str">
         <v>屋島地区コミュニティ協議会</v>
@@ -1691,7 +1691,7 @@
         <v>13.3</v>
       </c>
       <c r="R22" t="str">
-        <v>315</v>
+        <v>819</v>
       </c>
       <c r="S22" t="str">
         <v>前田校区コミュニティ協議会</v>
@@ -1750,7 +1750,7 @@
         <v>7.8</v>
       </c>
       <c r="R23" t="str">
-        <v>396</v>
+        <v>1173</v>
       </c>
       <c r="S23" t="str">
         <v>川添地区コミュニティ協議会</v>
@@ -1809,7 +1809,7 @@
         <v>13.8</v>
       </c>
       <c r="R24" t="str">
-        <v>315</v>
+        <v>1977</v>
       </c>
       <c r="S24" t="str">
         <v>林地区コミュニティ協議会</v>
@@ -1868,7 +1868,7 @@
         <v>28.4</v>
       </c>
       <c r="R25" t="str">
-        <v>234</v>
+        <v>758</v>
       </c>
       <c r="S25" t="str">
         <v>三谷地区コミュニティ協議会</v>
@@ -1927,7 +1927,7 @@
         <v>41.2</v>
       </c>
       <c r="R26" t="str">
-        <v>405</v>
+        <v>1012</v>
       </c>
       <c r="S26" t="str">
         <v>仏生山地区コミュニティ協議会</v>
@@ -1986,7 +1986,7 @@
         <v>25.2</v>
       </c>
       <c r="R27" t="str">
-        <v>315</v>
+        <v>2019</v>
       </c>
       <c r="S27" t="str">
         <v>多肥地区コミュニティ協議会</v>
@@ -2045,7 +2045,7 @@
         <v>33.5</v>
       </c>
       <c r="R28" t="str">
-        <v>405</v>
+        <v>1354</v>
       </c>
       <c r="S28" t="str">
         <v>一宮地区コミュニティ協議会</v>
@@ -2104,7 +2104,7 @@
         <v>38</v>
       </c>
       <c r="R29" t="str">
-        <v>301</v>
+        <v>1140</v>
       </c>
       <c r="S29" t="str">
         <v>円座校区コミュニティ協議会</v>
@@ -2163,7 +2163,7 @@
         <v>53.4</v>
       </c>
       <c r="R30" t="str">
-        <v>315</v>
+        <v>693</v>
       </c>
       <c r="S30" t="str">
         <v>川岡校区コミュニティ協議会</v>
@@ -2222,7 +2222,7 @@
         <v>26</v>
       </c>
       <c r="R31" t="str">
-        <v>405</v>
+        <v>954</v>
       </c>
       <c r="S31" t="str">
         <v>檀紙地区コミュニティ協議会</v>
@@ -2281,7 +2281,7 @@
         <v>7.1</v>
       </c>
       <c r="R32" t="str">
-        <v>405</v>
+        <v>1073</v>
       </c>
       <c r="S32" t="str">
         <v>弦打校区コミュニティ協議会</v>
@@ -2340,7 +2340,7 @@
         <v>21.9</v>
       </c>
       <c r="R33" t="str">
-        <v>315</v>
+        <v>724</v>
       </c>
       <c r="S33" t="str">
         <v>鬼無地区コミュニティ協議会</v>
@@ -2399,7 +2399,7 @@
         <v>2.3</v>
       </c>
       <c r="R34" t="str">
-        <v>464</v>
+        <v>1222</v>
       </c>
       <c r="S34" t="str">
         <v>香西地区コミュニティ協議会</v>
@@ -2458,7 +2458,7 @@
         <v>25.4</v>
       </c>
       <c r="R35" t="str">
-        <v>315</v>
+        <v>791</v>
       </c>
       <c r="S35" t="str">
         <v>下笠居地区コミュニティ協議会</v>
@@ -2517,7 +2517,7 @@
         <v>5.3</v>
       </c>
       <c r="R36" t="str">
-        <v>245</v>
+        <v>347</v>
       </c>
       <c r="S36" t="str">
         <v>女木地区コミュニティ協議会</v>
@@ -2576,7 +2576,7 @@
         <v>12.6</v>
       </c>
       <c r="R37" t="str">
-        <v>245</v>
+        <v>334</v>
       </c>
       <c r="S37" t="str">
         <v>男木地区コミュニティ協議会</v>
@@ -2635,7 +2635,7 @@
         <v>21.3</v>
       </c>
       <c r="R38" t="str">
-        <v>315</v>
+        <v>1040</v>
       </c>
       <c r="S38" t="str">
         <v>川島校区コミュニティ協議会</v>
@@ -2694,7 +2694,7 @@
         <v>18.1</v>
       </c>
       <c r="R39" t="str">
-        <v>315</v>
+        <v>1106</v>
       </c>
       <c r="S39" t="str">
         <v>十河校区コミュニティ協議会</v>
@@ -2753,7 +2753,7 @@
         <v>45.8</v>
       </c>
       <c r="R40" t="str">
-        <v>229</v>
+        <v>467</v>
       </c>
       <c r="S40" t="str">
         <v>植田校区コミュニティ協議会</v>
@@ -2812,7 +2812,7 @@
         <v>50.7</v>
       </c>
       <c r="R41" t="str">
-        <v>245</v>
+        <v>434</v>
       </c>
       <c r="S41" t="str">
         <v>東植田校区コミュニティ協議会</v>
@@ -2871,7 +2871,7 @@
         <v>323</v>
       </c>
       <c r="R42" t="str">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="S42" t="str">
         <v>東植田校区コミュニティ協議会</v>
@@ -2930,7 +2930,7 @@
         <v>6.2</v>
       </c>
       <c r="R43" t="str">
-        <v>390</v>
+        <v>1151</v>
       </c>
       <c r="S43" t="str">
         <v>栗林校区コミュニティ協議会</v>
@@ -2989,7 +2989,7 @@
         <v>2.1</v>
       </c>
       <c r="R44" t="str">
-        <v>477</v>
+        <v>1254</v>
       </c>
       <c r="S44" t="str">
         <v>亀阜校区コミュニティ協議会</v>
@@ -3048,7 +3048,7 @@
         <v>1.6</v>
       </c>
       <c r="R45" t="str">
-        <v>504</v>
+        <v>1339</v>
       </c>
       <c r="S45" t="str">
         <v>花園地区コミュニティ協議会</v>
@@ -3107,7 +3107,7 @@
         <v>3.1</v>
       </c>
       <c r="R46" t="str">
-        <v>721</v>
+        <v>2407</v>
       </c>
       <c r="S46" t="str">
         <v>松島地区コミュニティ協議会</v>
@@ -3225,7 +3225,7 @@
         <v>1.8</v>
       </c>
       <c r="R48" t="str">
-        <v>362</v>
+        <v>1223</v>
       </c>
       <c r="S48" t="str">
         <v>屋島地区コミュニティ協議会</v>
@@ -3284,7 +3284,7 @@
         <v>7.6</v>
       </c>
       <c r="R49" t="str">
-        <v>366</v>
+        <v>999</v>
       </c>
       <c r="S49" t="str">
         <v>川添地区コミュニティ協議会</v>
@@ -3343,7 +3343,7 @@
         <v>32</v>
       </c>
       <c r="R50" t="str">
-        <v>354</v>
+        <v>1252</v>
       </c>
       <c r="S50" t="str">
         <v>多肥地区コミュニティ協議会</v>
@@ -3402,7 +3402,7 @@
         <v>2.6</v>
       </c>
       <c r="R51" t="str">
-        <v>360</v>
+        <v>1246</v>
       </c>
       <c r="S51" t="str">
         <v>香西地区コミュニティ協議会</v>
@@ -3461,7 +3461,7 @@
         <v>32.3</v>
       </c>
       <c r="R52" t="str">
-        <v>396</v>
+        <v>908</v>
       </c>
       <c r="S52" t="str">
         <v>一宮地区コミュニティ協議会</v>
@@ -3520,7 +3520,7 @@
         <v>30.3</v>
       </c>
       <c r="R53" t="str">
-        <v>354</v>
+        <v>1241</v>
       </c>
       <c r="S53" t="str">
         <v>円座校区コミュニティ協議会</v>
@@ -3579,7 +3579,7 @@
         <v>32</v>
       </c>
       <c r="R54" t="str">
-        <v>396</v>
+        <v>680</v>
       </c>
       <c r="S54" t="str">
         <v>下笠居地区コミュニティ協議会</v>
@@ -3638,7 +3638,7 @@
         <v>25.4</v>
       </c>
       <c r="R55" t="str">
-        <v>362</v>
+        <v>1259</v>
       </c>
       <c r="S55" t="str">
         <v>川島校区コミュニティ協議会</v>
@@ -3697,7 +3697,7 @@
         <v>18.9</v>
       </c>
       <c r="R56" t="str">
-        <v>439</v>
+        <v>1158</v>
       </c>
       <c r="S56" t="str">
         <v>太田南地区コミュニティ協議会</v>
@@ -3756,7 +3756,7 @@
         <v>2.5</v>
       </c>
       <c r="R57" t="str">
-        <v>345</v>
+        <v>1335</v>
       </c>
       <c r="S57" t="str">
         <v>古高松地区コミュニティ協議会</v>
@@ -3815,7 +3815,7 @@
         <v>5.8</v>
       </c>
       <c r="R58" t="str">
-        <v>345</v>
+        <v>1114</v>
       </c>
       <c r="S58" t="str">
         <v>木太地区コミュニティ協議会</v>
@@ -3933,7 +3933,7 @@
         <v>5.2</v>
       </c>
       <c r="R60" t="str">
-        <v>953</v>
+        <v>2059</v>
       </c>
       <c r="S60" t="str">
         <v>栗林校区コミュニティ協議会</v>
@@ -6588,7 +6588,7 @@
         <v>31.8</v>
       </c>
       <c r="R105" t="str">
-        <v>452</v>
+        <v>1143</v>
       </c>
       <c r="S105" t="str">
         <v>むれコミュニティ協議会</v>
@@ -6765,7 +6765,7 @@
         <v>12.6</v>
       </c>
       <c r="R108" t="str">
-        <v>318</v>
+        <v>888</v>
       </c>
       <c r="S108" t="str">
         <v>むれコミュニティ協議会</v>
@@ -6824,7 +6824,7 @@
         <v>15.1</v>
       </c>
       <c r="R109" t="str">
-        <v>348</v>
+        <v>818</v>
       </c>
       <c r="S109" t="str">
         <v>むれコミュニティ協議会</v>
@@ -6942,7 +6942,7 @@
         <v>13.3</v>
       </c>
       <c r="R111" t="str">
-        <v>261</v>
+        <v>682</v>
       </c>
       <c r="S111" t="str">
         <v>むれコミュニティ協議会</v>
@@ -7237,7 +7237,7 @@
         <v>2.7</v>
       </c>
       <c r="R116" t="str">
-        <v>441</v>
+        <v>726</v>
       </c>
       <c r="S116" t="str">
         <v>庵治地区コミュニティ協議会</v>
@@ -7296,7 +7296,7 @@
         <v>2.1</v>
       </c>
       <c r="R117" t="str">
-        <v>243</v>
+        <v>681</v>
       </c>
       <c r="S117" t="str">
         <v>庵治地区コミュニティ協議会</v>
@@ -7591,7 +7591,7 @@
         <v>2.7</v>
       </c>
       <c r="R122" t="str">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="S122" t="str">
         <v>庵治地区コミュニティ協議会</v>
@@ -7709,7 +7709,7 @@
         <v>57</v>
       </c>
       <c r="R124" t="str">
-        <v>336</v>
+        <v>853</v>
       </c>
       <c r="S124" t="str">
         <v>大野校区コミュニティ協議会</v>
@@ -7768,7 +7768,7 @@
         <v>74.9</v>
       </c>
       <c r="R125" t="str">
-        <v>336</v>
+        <v>914</v>
       </c>
       <c r="S125" t="str">
         <v>浅野校区コミュニティ協議会</v>
@@ -8004,7 +8004,7 @@
         <v>87.1</v>
       </c>
       <c r="R129" t="str">
-        <v>336</v>
+        <v>825</v>
       </c>
       <c r="S129" t="str">
         <v>川東校区コミュニティ協議会</v>
@@ -8299,7 +8299,7 @@
         <v>93</v>
       </c>
       <c r="R134" t="str">
-        <v>285</v>
+        <v>821</v>
       </c>
       <c r="S134" t="str">
         <v>香南地区コミュニティ協議会</v>
@@ -8358,7 +8358,7 @@
         <v>89.1</v>
       </c>
       <c r="R135" t="str">
-        <v>485</v>
+        <v>814</v>
       </c>
       <c r="S135" t="str">
         <v>香南地区コミュニティ協議会</v>
@@ -8948,7 +8948,7 @@
         <v>175</v>
       </c>
       <c r="R145" t="str">
-        <v>897</v>
+        <v>1258</v>
       </c>
       <c r="S145" t="str">
         <v>塩江地区コミュニティ協議会</v>
@@ -9184,7 +9184,7 @@
         <v>23.5</v>
       </c>
       <c r="R149" t="str">
-        <v>297</v>
+        <v>1122</v>
       </c>
       <c r="S149" t="str">
         <v>国分寺北部校区コミュニティ協議会</v>
@@ -9243,7 +9243,7 @@
         <v>26.5</v>
       </c>
       <c r="R150" t="str">
-        <v>383</v>
+        <v>1231</v>
       </c>
       <c r="S150" t="str">
         <v>国分寺北部校区コミュニティ協議会</v>
@@ -9656,7 +9656,7 @@
         <v>28.9</v>
       </c>
       <c r="R157" t="str">
-        <v>405</v>
+        <v>1334</v>
       </c>
       <c r="S157" t="str">
         <v>国分寺南部校区コミュニティ協議会</v>
@@ -10659,7 +10659,7 @@
         <v>98</v>
       </c>
       <c r="R174" t="str">
-        <v>540</v>
+        <v>1465</v>
       </c>
       <c r="S174" t="str">
         <v>浅野校区コミュニティ協議会</v>
